--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FAUSTO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B100F900-5006-4348-9168-EBE01C6EFD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{840609F0-BFCB-455B-A41B-A20FB53A32B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GO Ordenamiento" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,11 @@
     <sheet name="GO Logistica Desalojos" sheetId="10" r:id="rId10"/>
     <sheet name="GO Logistica Cableado" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,6 +37,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="125">
   <si>
     <t>Mes</t>
   </si>
@@ -68,102 +72,114 @@
     <t>SLA BA Colaborativa</t>
   </si>
   <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>Buzon</t>
+  </si>
+  <si>
+    <t>Cableado</t>
+  </si>
+  <si>
+    <t>Puestos de Diarios</t>
+  </si>
+  <si>
+    <t>Puestos de Flores</t>
+  </si>
+  <si>
+    <t>Estructura publicitaria</t>
+  </si>
+  <si>
+    <t>Garitas</t>
+  </si>
+  <si>
+    <t>Bicicleteros</t>
+  </si>
+  <si>
+    <t>Areas gastronómicas (decks + mesas y sillas)</t>
+  </si>
+  <si>
+    <t>Anclajes</t>
+  </si>
+  <si>
+    <t>Local Comercial</t>
+  </si>
+  <si>
+    <t>Venta ambulante / manteros</t>
+  </si>
+  <si>
+    <t>LIMP. E HIG. ESP. PUB. ASENTAMIEN. PREC.</t>
+  </si>
+  <si>
+    <t>Comuna</t>
+  </si>
+  <si>
+    <t>Ingresados</t>
+  </si>
+  <si>
+    <t>Verificados</t>
+  </si>
+  <si>
+    <t>Cobertura</t>
+  </si>
+  <si>
+    <t>Comuna 1</t>
+  </si>
+  <si>
+    <t>Comuna 2</t>
+  </si>
+  <si>
+    <t>Comuna 3</t>
+  </si>
+  <si>
+    <t>NO SE PLANIFICÓ</t>
+  </si>
+  <si>
+    <t>Comuna 4</t>
+  </si>
+  <si>
+    <t>Comuna 5</t>
+  </si>
+  <si>
+    <t>Comuna 6</t>
+  </si>
+  <si>
+    <t>Comuna 7</t>
+  </si>
+  <si>
+    <t>Comuna 8</t>
+  </si>
+  <si>
+    <t>Comuna 9</t>
+  </si>
+  <si>
+    <t>Comuna 10</t>
+  </si>
+  <si>
+    <t>Comuna 11</t>
+  </si>
+  <si>
+    <t>Comuna 12</t>
+  </si>
+  <si>
+    <t>Comuna 13</t>
+  </si>
+  <si>
+    <t>Comuna 14</t>
+  </si>
+  <si>
+    <t>Comuna 15</t>
+  </si>
+  <si>
+    <t>Relevamiento</t>
+  </si>
+  <si>
+    <t>Avance %</t>
+  </si>
+  <si>
     <t>2026-07</t>
   </si>
   <si>
-    <t>Buzon</t>
-  </si>
-  <si>
-    <t>Cableado</t>
-  </si>
-  <si>
-    <t>Puestos de Diarios</t>
-  </si>
-  <si>
-    <t>Puestos de Flores</t>
-  </si>
-  <si>
-    <t>Estructura publicitaria</t>
-  </si>
-  <si>
-    <t>Garitas</t>
-  </si>
-  <si>
-    <t>Bicicleteros</t>
-  </si>
-  <si>
-    <t>Anclajes</t>
-  </si>
-  <si>
-    <t>Local Comercial</t>
-  </si>
-  <si>
-    <t>Venta ambulante / manteros</t>
-  </si>
-  <si>
-    <t>Comuna</t>
-  </si>
-  <si>
-    <t>Ingresados</t>
-  </si>
-  <si>
-    <t>Verificados</t>
-  </si>
-  <si>
-    <t>Cobertura</t>
-  </si>
-  <si>
-    <t>Comuna 1</t>
-  </si>
-  <si>
-    <t>Comuna 2</t>
-  </si>
-  <si>
-    <t>Comuna 3</t>
-  </si>
-  <si>
-    <t>Comuna 4</t>
-  </si>
-  <si>
-    <t>Comuna 5</t>
-  </si>
-  <si>
-    <t>Comuna 6</t>
-  </si>
-  <si>
-    <t>Comuna 7</t>
-  </si>
-  <si>
-    <t>Comuna 8</t>
-  </si>
-  <si>
-    <t>Comuna 9</t>
-  </si>
-  <si>
-    <t>Comuna 10</t>
-  </si>
-  <si>
-    <t>Comuna 11</t>
-  </si>
-  <si>
-    <t>Comuna 12</t>
-  </si>
-  <si>
-    <t>Comuna 13</t>
-  </si>
-  <si>
-    <t>Comuna 14</t>
-  </si>
-  <si>
-    <t>Comuna 15</t>
-  </si>
-  <si>
-    <t>Relevamiento</t>
-  </si>
-  <si>
-    <t>Avance %</t>
-  </si>
-  <si>
     <t>Indicador</t>
   </si>
   <si>
@@ -185,6 +201,9 @@
     <t>Grupo</t>
   </si>
   <si>
+    <t>Corredor Norte</t>
+  </si>
+  <si>
     <t>Resto de CABA</t>
   </si>
   <si>
@@ -203,217 +222,205 @@
     <t>Cantidad Secuestros</t>
   </si>
   <si>
+    <t>Barrio 31</t>
+  </si>
+  <si>
+    <t>GOVNA, GOIEP, GO Ord</t>
+  </si>
+  <si>
+    <t>Se retiran 10 carros, 1355 productos a la venta y se realiza un ordenamiento en general de la zona</t>
+  </si>
+  <si>
+    <t>10 carros ; 1355 productos</t>
+  </si>
+  <si>
+    <t>GOIEP, Policia</t>
+  </si>
+  <si>
+    <t>Se retiran 2 ranchada,s se desplazan 3 personas en situación de calle. Se colecta unos cartones, cajas de carton, un colchon inflable, tres colchones, almohadones, almohadas, zapatillas, lonas, cortinas,sábanas, metales, cables de cobre, una silla, una mesa de madera, cajas de madera,chapas, 7 carros, fierros,gran cantidad de basuras varias.</t>
+  </si>
+  <si>
+    <t>2 ranchadas ; colchón inflable ; 3 colchones ; 1 silla ; 1 mesa ; 7 carros ; (+ropa, almohadones, carton, metal, lonas, cortinas, sabanas, etc).</t>
+  </si>
+  <si>
+    <t>1 11 14</t>
+  </si>
+  <si>
+    <t>GOIEP, GO Ord, GOVNA, Policia</t>
+  </si>
+  <si>
+    <t>Se retiran 17 colchones, 1 bolsón, mantas, cartones, ropa, juguetes, sillas y nylons. Se desplazan 8 personas.</t>
+  </si>
+  <si>
+    <t>17 colchones ; 1 bolsón ; mantas ; cartones ; ropa ; juguetes ; sillas ; basura</t>
+  </si>
+  <si>
+    <t>GOIEP, GOPYG, GOVNA, GO Ord, Policia</t>
+  </si>
+  <si>
+    <t>Se retira un container utilizado como depósito, 2 construcciones de material clandestinas, 7 carros, 7 auutos en estado de abandono, una casilla donde vivía gente y basura en general</t>
+  </si>
+  <si>
+    <t>1 container ; 2 construcciones ; 7 carros ; 7 autos ; 1 casilla vivienda ; basura</t>
+  </si>
+  <si>
+    <t>21-24 Zavaleta</t>
+  </si>
+  <si>
+    <t>GOIEP, Policia, Ente</t>
+  </si>
+  <si>
+    <t>Se retiran 3 bolsones, se desarma una estructura de ranchada, Se levantan cartones, maderas, metales. sillones, mantas y baldes. Se desplazan 8 personas.</t>
+  </si>
+  <si>
+    <t>3 bolsones ; 1 ranchada ; cartones ; maderas ; metales ; sillones ; mantas ; baldes.</t>
+  </si>
+  <si>
+    <t>GOVNA, GO Ord, GOIEP, Tránsito, Ente, Policia</t>
+  </si>
+  <si>
+    <t>Se retiran parrillas, mesas, carro, indumentaria y artículos varios. Además, se desplazan 4 personas y se levantan 4 colchones y basura en general</t>
+  </si>
+  <si>
+    <t>4 ranchadas ; 358 artículos ; 1 parrilla ; 1 carro ; mesas ; basura</t>
+  </si>
+  <si>
+    <t>GOIEP, GO Ord, GOVNA, Policia, Ente</t>
+  </si>
+  <si>
+    <t>Se retiran 5 parrillas, 1 puesto de comida anclado en el piso, 1 foodtruck, palets, mantas, reposeras, chapas, escobas, sillas, muebles, 1 bicicleta, ropa, ruedas, lonas, elementos de nylon y metal y residuos varios. Se desplazan 16 personas, se levantan 12 ranchadas, 12 colchones, 6 carros y 1 bolsón. Se secuestran elementos de vendedor de chipa, mercadería por ocupación de 1 verdulería y 1 bazar</t>
+  </si>
+  <si>
+    <t>5 parrillas ; 12 ranchadas ; 12 colchones ; 6 carros ; 1 bolsón ; 1 foodtruck ; 1 puesto ; 1 bicicleta ; ropa/telas ; palets ; sillas ; basura</t>
+  </si>
+  <si>
+    <t>Barrio 20</t>
+  </si>
+  <si>
+    <t>Se levanta 1 ranchada grande, tablas de madera, muebles, metales, baldes, latas, sillas, caños de luz, botellas, y basura. Se identifica y requisa a 10 adultos.</t>
+  </si>
+  <si>
+    <t>1 ranchada ; muebles ; maderas y metales ; basura</t>
+  </si>
+  <si>
+    <t>GOIEP, GO Ord, GOVNA, UPE, Policia, Tránsito</t>
+  </si>
+  <si>
+    <t>Se levantan ranchadas, 12 carros, parrillas, estructuras metálicas, muebles y estructuras de electrodomésticos, además de lonas y basura. Se realiza el remolque de un automóvil y una moto. Se interviene en Sara Beatriz por venta no autorizada.</t>
+  </si>
+  <si>
+    <t>12 carros ; ranchada ; parrillas ; estrucutras metálicas ; automóvil ; moto ; telas ; basura</t>
+  </si>
+  <si>
+    <t>La Carbonilla</t>
+  </si>
+  <si>
+    <t>Se retira un food truck, un puesto de diarios en desuso, estructuras utilizadas como cocheras, elementos para reservar lugar, estructuras metálicas y una gran cantidad de bolsones de materiales. Se utilizaron 5 hidrogruas y 1 camion de basura</t>
+  </si>
+  <si>
+    <t>1 food truck ; 1 puesto diarios ; bolsones ; estructuras metálicas.</t>
+  </si>
+  <si>
     <t>Lugar</t>
   </si>
   <si>
     <t>Recursos</t>
   </si>
   <si>
+    <t>TRAFUL 3702 - 3706 / / ALBERTO EINSTEIN 503 - 507 - 509</t>
+  </si>
+  <si>
+    <t>8 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>URIARTE 2440</t>
+  </si>
+  <si>
+    <t>8 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>OLAVARRIA 351</t>
+  </si>
+  <si>
+    <t>8 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>LONDRES 4255</t>
+  </si>
+  <si>
+    <t>TERRERO 127 (JUDICIAL)</t>
+  </si>
+  <si>
+    <t>NICETO VEGA 5404 (JUDICIAL)</t>
+  </si>
+  <si>
+    <t>8 - OPERARIO / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - MINICARGADORA (BODCAT) / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>CARLOS MELO 535 - 539</t>
+  </si>
+  <si>
+    <t>8 - OPERARIO / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>VIRREY LORETO 3416</t>
+  </si>
+  <si>
+    <t>3 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS</t>
+  </si>
+  <si>
+    <t>ALBERTI 565 - 567 - 569 - 571</t>
+  </si>
+  <si>
+    <t>8 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI / 1 - CAMION SEMI / 1 - CAMION SEMI / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>CESAR DIAZ 2979 (JUDICIAL)</t>
+  </si>
+  <si>
+    <t>NEPPER 1088</t>
+  </si>
+  <si>
+    <t>LAUTARO 1607</t>
+  </si>
+  <si>
+    <t>6 - OPERARIO / 4 - OPERARIO / 4 - OPERARIO / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>ATUEL 255</t>
+  </si>
+  <si>
+    <t>10 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMION SEMI / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>PASAJE LA FACULTAD 1873</t>
+  </si>
+  <si>
+    <t>CARLOS CALVO 550</t>
+  </si>
+  <si>
+    <t>10 - OPERARIO / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 2 - CAMION BATEA / 1 - CAMIONETA USO GENERAL</t>
+  </si>
+  <si>
+    <t>ROCHA Y HERNANDARIAS - MPF</t>
+  </si>
+  <si>
+    <t>MANSILLA 2529</t>
+  </si>
+  <si>
+    <t>SANTOS DUPONT 2790</t>
+  </si>
+  <si>
+    <t>10 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - REMOLQUE TIPO PLANCHA / 1 - CAMION SEMI</t>
+  </si>
+  <si>
+    <t>SALVADOR 4641 - 4643 / AGUERO 370</t>
+  </si>
+  <si>
+    <t>CUENCA 41</t>
+  </si>
+  <si>
     <t>Planificado</t>
-  </si>
-  <si>
-    <t>2026-06</t>
-  </si>
-  <si>
-    <t>Areas gastronómicas (decks + mesas y sillas)</t>
-  </si>
-  <si>
-    <t>NO SE PLANIFICÓ</t>
-  </si>
-  <si>
-    <t>Corredor Norte</t>
-  </si>
-  <si>
-    <t>Barrio 31</t>
-  </si>
-  <si>
-    <t>GOVNA, GOIEP, GO Ord</t>
-  </si>
-  <si>
-    <t>Se retiran 10 carros, 1355 productos a la venta y se realiza un ordenamiento en general de la zona</t>
-  </si>
-  <si>
-    <t>10 carros ; 1355 productos</t>
-  </si>
-  <si>
-    <t>GOIEP, Policia</t>
-  </si>
-  <si>
-    <t>Se retiran 2 ranchada,s se desplazan 3 personas en situación de calle. Se colecta unos cartones, cajas de carton, un colchon inflable, tres colchones, almohadones, almohadas, zapatillas, lonas, cortinas,sábanas, metales, cables de cobre, una silla, una mesa de madera, cajas de madera,chapas, 7 carros, fierros,gran cantidad de basuras varias.</t>
-  </si>
-  <si>
-    <t>2 ranchadas ; colchón inflable ; 3 colchones ; 1 silla ; 1 mesa ; 7 carros ; (+ropa, almohadones, carton, metal, lonas, cortinas, sabanas, etc).</t>
-  </si>
-  <si>
-    <t>1 11 14</t>
-  </si>
-  <si>
-    <t>GOIEP, GO Ord, GOVNA, Policia</t>
-  </si>
-  <si>
-    <t>Se retiran 17 colchones, 1 bolsón, mantas, cartones, ropa, juguetes, sillas y nylons. Se desplazan 8 personas.</t>
-  </si>
-  <si>
-    <t>17 colchones ; 1 bolsón ; mantas ; cartones ; ropa ; juguetes ; sillas ; basura</t>
-  </si>
-  <si>
-    <t>GOIEP, GOPYG, GOVNA, GO Ord, Policia</t>
-  </si>
-  <si>
-    <t>Se retira un container utilizado como depósito, 2 construcciones de material clandestinas, 7 carros, 7 auutos en estado de abandono, una casilla donde vivía gente y basura en general</t>
-  </si>
-  <si>
-    <t>1 container ; 2 construcciones ; 7 carros ; 7 autos ; 1 casilla vivienda ; basura</t>
-  </si>
-  <si>
-    <t>21-24 Zavaleta</t>
-  </si>
-  <si>
-    <t>GOIEP, Policia, Ente</t>
-  </si>
-  <si>
-    <t>Se retiran 3 bolsones, se desarma una estructura de ranchada, Se levantan cartones, maderas, metales. sillones, mantas y baldes. Se desplazan 8 personas.</t>
-  </si>
-  <si>
-    <t>3 bolsones ; 1 ranchada ; cartones ; maderas ; metales ; sillones ; mantas ; baldes.</t>
-  </si>
-  <si>
-    <t>GOVNA, GO Ord, GOIEP, Tránsito, Ente, Policia</t>
-  </si>
-  <si>
-    <t>Se retiran parrillas, mesas, carro, indumentaria y artículos varios. Además, se desplazan 4 personas y se levantan 4 colchones y basura en general</t>
-  </si>
-  <si>
-    <t>4 ranchadas ; 358 artículos ; 1 parrilla ; 1 carro ; mesas ; basura</t>
-  </si>
-  <si>
-    <t>GOIEP, GO Ord, GOVNA, Policia, Ente</t>
-  </si>
-  <si>
-    <t>Se retiran 5 parrillas, 1 puesto de comida anclado en el piso, 1 foodtruck, palets, mantas, reposeras, chapas, escobas, sillas, muebles, 1 bicicleta, ropa, ruedas, lonas, elementos de nylon y metal y residuos varios. Se desplazan 16 personas, se levantan 12 ranchadas, 12 colchones, 6 carros y 1 bolsón. Se secuestran elementos de vendedor de chipa, mercadería por ocupación de 1 verdulería y 1 bazar</t>
-  </si>
-  <si>
-    <t>5 parrillas ; 12 ranchadas ; 12 colchones ; 6 carros ; 1 bolsón ; 1 foodtruck ; 1 puesto ; 1 bicicleta ; ropa/telas ; palets ; sillas ; basura</t>
-  </si>
-  <si>
-    <t>Barrio 20</t>
-  </si>
-  <si>
-    <t>Se levanta 1 ranchada grande, tablas de madera, muebles, metales, baldes, latas, sillas, caños de luz, botellas, y basura. Se identifica y requisa a 10 adultos.</t>
-  </si>
-  <si>
-    <t>1 ranchada ; muebles ; maderas y metales ; basura</t>
-  </si>
-  <si>
-    <t>GOIEP, GO Ord, GOVNA, UPE, Policia, Tránsito</t>
-  </si>
-  <si>
-    <t>Se levantan ranchadas, 12 carros, parrillas, estructuras metálicas, muebles y estructuras de electrodomésticos, además de lonas y basura. Se realiza el remolque de un automóvil y una moto. Se interviene en Sara Beatriz por venta no autorizada.</t>
-  </si>
-  <si>
-    <t>12 carros ; ranchada ; parrillas ; estrucutras metálicas ; automóvil ; moto ; telas ; basura</t>
-  </si>
-  <si>
-    <t>La Carbonilla</t>
-  </si>
-  <si>
-    <t>Se retira un food truck, un puesto de diarios en desuso, estructuras utilizadas como cocheras, elementos para reservar lugar, estructuras metálicas y una gran cantidad de bolsones de materiales. Se utilizaron 5 hidrogruas y 1 camion de basura</t>
-  </si>
-  <si>
-    <t>1 food truck ; 1 puesto diarios ; bolsones ; estructuras metálicas.</t>
-  </si>
-  <si>
-    <t>TRAFUL 3702 - 3706 / / ALBERTO EINSTEIN 503 - 507 - 509</t>
-  </si>
-  <si>
-    <t>8 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>URIARTE 2440</t>
-  </si>
-  <si>
-    <t>8 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>OLAVARRIA 351</t>
-  </si>
-  <si>
-    <t>8 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>LONDRES 4255</t>
-  </si>
-  <si>
-    <t>TERRERO 127 (JUDICIAL)</t>
-  </si>
-  <si>
-    <t>NICETO VEGA 5404 (JUDICIAL)</t>
-  </si>
-  <si>
-    <t>8 - OPERARIO / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - MINICARGADORA (BODCAT) / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>CARLOS MELO 535 - 539</t>
-  </si>
-  <si>
-    <t>8 - OPERARIO / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>VIRREY LORETO 3416</t>
-  </si>
-  <si>
-    <t>3 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS</t>
-  </si>
-  <si>
-    <t>ALBERTI 565 - 567 - 569 - 571</t>
-  </si>
-  <si>
-    <t>8 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI / 1 - CAMION SEMI / 1 - CAMION SEMI / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>CESAR DIAZ 2979 (JUDICIAL)</t>
-  </si>
-  <si>
-    <t>NEPPER 1088</t>
-  </si>
-  <si>
-    <t>LAUTARO 1607</t>
-  </si>
-  <si>
-    <t>6 - OPERARIO / 4 - OPERARIO / 4 - OPERARIO / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - CAMION SEMI / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>ATUEL 255</t>
-  </si>
-  <si>
-    <t>10 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - CAMION SEMI / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>PASAJE LA FACULTAD 1873</t>
-  </si>
-  <si>
-    <t>CARLOS CALVO 550</t>
-  </si>
-  <si>
-    <t>10 - OPERARIO / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 2 - CAMION BATEA / 1 - CAMIONETA USO GENERAL</t>
-  </si>
-  <si>
-    <t>ROCHA Y HERNANDARIAS - MPF</t>
-  </si>
-  <si>
-    <t>MANSILLA 2529</t>
-  </si>
-  <si>
-    <t>SANTOS DUPONT 2790</t>
-  </si>
-  <si>
-    <t>10 - OPERARIO / 1 - CAMIONETA USO GENERAL / 1 - CAMIONETA USO GENERAL / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - HIDROGRUA 25tn C / HERRAMIENTAS / 1 - REMOLQUE TIPO PLANCHA / 1 - CAMION SEMI</t>
-  </si>
-  <si>
-    <t>SALVADOR 4641 - 4643 / AGUERO 370</t>
-  </si>
-  <si>
-    <t>CUENCA 41</t>
   </si>
 </sst>
 </file>
@@ -750,7 +757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
@@ -789,7 +796,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2">
         <v>20</v>
@@ -815,7 +822,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2">
         <v>20</v>
@@ -841,7 +848,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
         <v>90</v>
@@ -867,7 +874,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2">
         <v>90</v>
@@ -893,7 +900,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2">
         <v>15</v>
@@ -919,7 +926,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2">
         <v>10</v>
@@ -945,7 +952,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
         <v>10</v>
@@ -971,13 +978,13 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>101</v>
@@ -997,13 +1004,13 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2">
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2">
         <v>158</v>
@@ -1023,13 +1030,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2">
         <v>45</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="2">
         <v>107</v>
@@ -1055,7 +1062,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1067,18 +1074,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="8">
         <v>46174</v>
@@ -1092,7 +1099,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B3" s="9">
         <v>46175</v>
@@ -1106,7 +1113,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B4" s="9">
         <v>46176</v>
@@ -1120,7 +1127,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B5" s="9">
         <v>46177</v>
@@ -1134,7 +1141,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9">
         <v>46177</v>
@@ -1148,7 +1155,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B7" s="9">
         <v>46178</v>
@@ -1162,7 +1169,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B8" s="9">
         <v>46182</v>
@@ -1176,7 +1183,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B9" s="9">
         <v>46183</v>
@@ -1190,7 +1197,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B10" s="9">
         <v>46183</v>
@@ -1204,7 +1211,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B11" s="9">
         <v>46183</v>
@@ -1218,7 +1225,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B12" s="9">
         <v>46185</v>
@@ -1232,7 +1239,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B13" s="9">
         <v>46185</v>
@@ -1246,7 +1253,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B14" s="9">
         <v>46189</v>
@@ -1260,7 +1267,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B15" s="9">
         <v>46190</v>
@@ -1274,7 +1281,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B16" s="9">
         <v>46192</v>
@@ -1288,7 +1295,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B17" s="9">
         <v>46196</v>
@@ -1302,7 +1309,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B18" s="9">
         <v>46196</v>
@@ -1316,7 +1323,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B19" s="9">
         <v>46198</v>
@@ -1330,7 +1337,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B20" s="9">
         <v>46202</v>
@@ -1344,7 +1351,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B21" s="9">
         <v>46203</v>
@@ -1364,7 +1371,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1376,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -1384,7 +1391,7 @@
     </row>
     <row r="2" spans="1:3" ht="15">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="11">
         <v>946</v>
@@ -1401,7 +1408,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
@@ -1440,29 +1447,27 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2">
         <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2">
+        <v>52</v>
+      </c>
+      <c r="E2" s="2">
         <v>51</v>
       </c>
-      <c r="E2" s="2">
-        <v>50</v>
-      </c>
       <c r="F2" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.38</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1472,7 +1477,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
@@ -1514,20 +1519,22 @@
         <v>8</v>
       </c>
       <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="D2" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3">
         <v>0</v>
@@ -1541,7 +1548,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1555,24 +1562,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2">
         <v>442</v>
@@ -1587,10 +1594,10 @@
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2">
         <v>312</v>
@@ -1605,16 +1612,16 @@
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
@@ -1623,16 +1630,16 @@
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
@@ -1641,16 +1648,16 @@
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
@@ -1659,10 +1666,10 @@
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2">
         <v>288</v>
@@ -1677,16 +1684,16 @@
     </row>
     <row r="8" spans="1:5" ht="15">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
@@ -1695,16 +1702,16 @@
     </row>
     <row r="9" spans="1:5" ht="15">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
@@ -1713,16 +1720,16 @@
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
@@ -1731,16 +1738,16 @@
     </row>
     <row r="11" spans="1:5" ht="15">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E11" s="4">
         <f t="shared" si="0"/>
@@ -1749,16 +1756,16 @@
     </row>
     <row r="12" spans="1:5" ht="15">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
@@ -1767,16 +1774,16 @@
     </row>
     <row r="13" spans="1:5" ht="15">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
@@ -1785,10 +1792,10 @@
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2">
         <v>603</v>
@@ -1803,10 +1810,10 @@
     </row>
     <row r="15" spans="1:5" ht="15">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2">
         <v>1046</v>
@@ -1821,10 +1828,10 @@
     </row>
     <row r="16" spans="1:5" ht="15">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2">
         <v>460</v>
@@ -1845,7 +1852,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -1857,15 +1864,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3">
@@ -1880,7 +1887,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1892,15 +1899,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1913,7 +1920,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1926,21 +1933,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2">
         <v>147</v>
@@ -1951,10 +1958,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2">
         <v>3</v>
@@ -1965,10 +1972,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2">
         <v>212</v>
@@ -1979,10 +1986,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2">
         <v>61</v>
@@ -1993,10 +2000,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
@@ -2007,10 +2014,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
@@ -2021,10 +2028,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2">
         <v>211</v>
@@ -2035,10 +2042,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -2049,10 +2056,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2">
         <v>77</v>
@@ -2063,10 +2070,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2">
         <v>78</v>
@@ -2077,10 +2084,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -2091,10 +2098,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
@@ -2105,10 +2112,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2">
         <v>184</v>
@@ -2119,10 +2126,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2">
         <v>61</v>
@@ -2133,10 +2140,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2">
         <v>24</v>
@@ -2153,7 +2160,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2166,24 +2173,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2">
         <v>2849</v>
@@ -2192,15 +2199,15 @@
         <v>2346</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2">
         <v>1043</v>
@@ -2209,15 +2216,15 @@
         <v>569</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2">
         <v>136</v>
@@ -2226,15 +2233,15 @@
         <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2">
         <v>141</v>
@@ -2243,15 +2250,15 @@
         <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2">
         <v>116</v>
@@ -2260,15 +2267,15 @@
         <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2">
         <v>24</v>
@@ -2277,15 +2284,15 @@
         <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2">
         <v>36</v>
@@ -2294,15 +2301,15 @@
         <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2">
         <v>55</v>
@@ -2311,15 +2318,15 @@
         <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2">
         <v>15</v>
@@ -2328,15 +2335,15 @@
         <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2">
         <v>16</v>
@@ -2345,15 +2352,15 @@
         <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2">
         <v>14</v>
@@ -2362,15 +2369,15 @@
         <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" s="2">
         <v>80</v>
@@ -2379,15 +2386,15 @@
         <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2">
         <v>844</v>
@@ -2396,15 +2403,15 @@
         <v>562</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2">
         <v>1238</v>
@@ -2413,15 +2420,15 @@
         <v>923</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2">
         <v>119</v>
@@ -2430,7 +2437,7 @@
         <v>88</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2441,7 +2448,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2456,219 +2463,219 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5">
         <v>46176</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6">
         <v>46177</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" t="s">
         <v>64</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6">
         <v>46182</v>
       </c>
       <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>68</v>
-      </c>
-      <c r="E4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6">
         <v>46184</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
         <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B6" s="6">
         <v>46190</v>
       </c>
       <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
         <v>74</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>75</v>
-      </c>
-      <c r="E6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6">
         <v>46191</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" t="s">
         <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B8" s="6">
         <v>46191</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
         <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6">
         <v>46196</v>
       </c>
       <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" t="s">
         <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B10" s="6">
         <v>46197</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" t="s">
         <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B11" s="6">
         <v>46203</v>
       </c>
       <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" t="s">
         <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
